--- a/exports/trend_1d/ENRIN_full_report.xlsx
+++ b/exports/trend_1d/ENRIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>16.37</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H2" t="n">
-        <v>3357.7</v>
+        <v>3236.4</v>
       </c>
       <c r="I2" t="n">
         <v>3267.337053636529</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K2" t="n">
-        <v>14.9</v>
+        <v>10.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -555,7 +578,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.17</v>
+        <v>3.61</v>
       </c>
       <c r="O2" t="n">
         <v>-0.98</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.69</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="H3" t="n">
-        <v>3296.1</v>
+        <v>3348.9</v>
       </c>
       <c r="I3" t="n">
         <v>3338.624969027725</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.84</v>
+        <v>-3.48</v>
       </c>
       <c r="L3" t="n">
-        <v>4.12</v>
+        <v>4.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="H4" t="n">
-        <v>3162.9</v>
+        <v>3097.5</v>
       </c>
       <c r="I4" t="n">
         <v>3106.537906805082</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.55</v>
+        <v>-7.51</v>
       </c>
       <c r="L4" t="n">
-        <v>8.220000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="M4" t="n">
         <v>0.47</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.89</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H5" t="n">
-        <v>2356.9</v>
+        <v>2481.5</v>
       </c>
       <c r="I5" t="n">
         <v>2416.189095513892</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
-        <v>23.91</v>
+        <v>19.89</v>
       </c>
       <c r="L5" t="n">
         <v>6.34</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="H6" t="n">
-        <v>2771.4</v>
+        <v>2629.4</v>
       </c>
       <c r="I6" t="n">
         <v>2643.008530296501</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K6" t="n">
-        <v>11.68</v>
+        <v>5.96</v>
       </c>
       <c r="L6" t="n">
         <v>5.28</v>
@@ -783,7 +854,7 @@
         <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.41</v>
+        <v>5.12</v>
       </c>
       <c r="O6" t="n">
         <v>5.29</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>14.35</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H7" t="n">
-        <v>2849.2</v>
+        <v>2918.3</v>
       </c>
       <c r="I7" t="n">
         <v>2904.992115865014</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.359999999999999</v>
+        <v>-10.99</v>
       </c>
       <c r="L7" t="n">
-        <v>9.720000000000001</v>
+        <v>11.77</v>
       </c>
       <c r="M7" t="n">
         <v>2.9</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.78</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="H8" t="n">
-        <v>3549.5</v>
+        <v>3281.5</v>
       </c>
       <c r="I8" t="n">
         <v>3405.289164749684</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K8" t="n">
-        <v>21.63</v>
+        <v>12.45</v>
       </c>
       <c r="L8" t="n">
         <v>1.62</v>
@@ -897,7 +992,7 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.03</v>
+        <v>7.55</v>
       </c>
       <c r="O8" t="n">
         <v>2.43</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>18.11</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="H9" t="n">
-        <v>3252.2</v>
+        <v>3648.8</v>
       </c>
       <c r="I9" t="n">
         <v>3465.43709812059</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>0.89</v>
+        <v>-11.19</v>
       </c>
       <c r="L9" t="n">
-        <v>8.67</v>
+        <v>13.82</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>6.08</v>
       </c>
       <c r="N9" t="n">
-        <v>4.23</v>
+        <v>12.19</v>
       </c>
       <c r="O9" t="n">
         <v>-7.55</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>13.99</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H10" t="n">
-        <v>3242.6</v>
+        <v>3229.6</v>
       </c>
       <c r="I10" t="n">
         <v>3238.2830318174</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>-11.13</v>
+        <v>-11.49</v>
       </c>
       <c r="L10" t="n">
-        <v>11.55</v>
+        <v>12.03</v>
       </c>
       <c r="M10" t="n">
         <v>0.16</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.69</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H11" t="n">
-        <v>3200</v>
+        <v>3334</v>
       </c>
       <c r="I11" t="n">
         <v>3329.607135825963</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" t="n">
-        <v>0.92</v>
+        <v>-3.23</v>
       </c>
       <c r="L11" t="n">
-        <v>3.67</v>
+        <v>3.98</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.82</v>
+        <v>4.19</v>
       </c>
       <c r="O11" t="n">
         <v>-0.4</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>12.45</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H12" t="n">
-        <v>3162.8</v>
+        <v>2957</v>
       </c>
       <c r="I12" t="n">
         <v>3016.631996539006</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.13</v>
+        <v>-11.31</v>
       </c>
       <c r="L12" t="n">
-        <v>9.82</v>
+        <v>11.64</v>
       </c>
       <c r="M12" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>6.51</v>
       </c>
       <c r="O12" t="n">
         <v>4.19</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1185,6 +1340,14 @@
       <c r="Q13" t="n">
         <v>9</v>
       </c>
+      <c r="R13" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1893,7 +2056,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="6">
@@ -1903,7 +2066,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1913,7 +2076,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -1923,7 +2086,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1933,7 +2096,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59.5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -1943,7 +2106,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -1953,7 +2116,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1963,7 +2126,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1973,7 +2136,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>45.5</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="14">
@@ -1983,7 +2146,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.81</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="15">
@@ -1993,7 +2156,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.4</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="16">
@@ -2003,7 +2166,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="17">
@@ -2013,7 +2176,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23.91</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="18">
@@ -2023,7 +2186,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.5</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="19">
@@ -2033,7 +2196,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.41</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="20">
@@ -2053,7 +2216,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.55</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="22">
@@ -2073,7 +2236,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2083,7 +2246,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="25">
@@ -2093,7 +2256,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.1</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="26">
@@ -2103,7 +2266,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.07</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="27">
@@ -2113,7 +2276,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.92</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="28">
@@ -2123,7 +2286,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
